--- a/POTAL_Feature_Audit_2603290000.xlsx
+++ b/POTAL_Feature_Audit_2603290000.xlsx
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -3166,14 +3166,14 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; B UPGRADED</t>
+          <t>D -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; B UPGRADED</t>
+          <t>D -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>C -&gt; B UPGRADED</t>
+          <t>C -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>C -&gt; B UPGRADED</t>
+          <t>C -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>❌ D</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>C -&gt; D</t>
+          <t>C -&gt; D → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; B UPGRADED</t>
+          <t>D -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; B UPGRADED</t>
+          <t>D -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>C -&gt; B UPGRADED</t>
+          <t>C -&gt; B UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>B -&gt; C</t>
+          <t>B -&gt; C → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; C UPGRADED</t>
+          <t>D -&gt; C UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>⚠️ B</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; C UPGRADED</t>
+          <t>D -&gt; C UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; C UPGRADED</t>
+          <t>D -&gt; C UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>B -&gt; C</t>
+          <t>B -&gt; C → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>📄 C</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>D -&gt; C UPGRADED</t>
+          <t>D -&gt; C UPGRADED → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7706,14 +7706,14 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>❌ D</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>C -&gt; D</t>
+          <t>C -&gt; D → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -7750,14 +7750,14 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>❌ D</t>
+          <t>✅ A</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>unchanged</t>
+          <t>unchanged → A UPGRADED</t>
         </is>
       </c>
     </row>
@@ -8301,23 +8301,23 @@
         <v>142</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
